--- a/ЛР2-3_Объем_рынка/Excel/SW_объем_рынка_Similarweb_NotaCode.xlsx
+++ b/ЛР2-3_Объем_рынка/Excel/SW_объем_рынка_Similarweb_NotaCode.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\ИИТ\ЭлектронныйБизнес\ЛР2-3_Объем_рынка\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ИИТ\ЭлектронныйБизнес\ЛР2-3_Объем_рынка\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{812582A0-CB09-4E85-A8AD-4F4222CF2FE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7441449-14AF-4C08-A853-3A2CDCDEB653}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7200" yWindow="3975" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="368" yWindow="368" windowWidth="12022" windowHeight="10972" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="11_Вариант_М2" sheetId="49" r:id="rId1"/>
-    <sheet name="10_TAM_SAM_SOM_М1" sheetId="48" r:id="rId2"/>
-    <sheet name="09_Концентрация" sheetId="47" r:id="rId3"/>
+    <sheet name="11_Вариант_М2" sheetId="52" r:id="rId1"/>
+    <sheet name="10_TAM_SAM_SOM_М1" sheetId="51" r:id="rId2"/>
+    <sheet name="09_Концентрация" sheetId="50" r:id="rId3"/>
     <sheet name="00_Методика" sheetId="1" r:id="rId4"/>
     <sheet name="01_Параметры" sheetId="2" r:id="rId5"/>
     <sheet name="02_Конкуренты_SW" sheetId="3" r:id="rId6"/>
@@ -27,6 +27,20 @@
     <sheet name="08_Источники" sheetId="9" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191029" refMode="R1C1"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -1589,7 +1603,7 @@
             <c:numRef>
               <c:f>'07_Дашборд'!$B$11:$B$13</c:f>
               <c:numCache>
-                <c:formatCode>#,##0\ \₽</c:formatCode>
+                <c:formatCode>#\ ##0\ \₽</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>7689.7210919760009</c:v>
@@ -1637,7 +1651,7 @@
             <c:numRef>
               <c:f>'07_Дашборд'!$C$11:$C$13</c:f>
               <c:numCache>
-                <c:formatCode>#,##0\ \₽</c:formatCode>
+                <c:formatCode>#\ ##0\ \₽</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>38.448605459880007</c:v>
@@ -1714,7 +1728,7 @@
             </a:ln>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="#,##0\ \₽" sourceLinked="1"/>
+        <c:numFmt formatCode="#\ ##0\ \₽" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -2316,12 +2330,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4360852B-C9B9-4D38-9D32-07669DE20458}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73ED5EEF-DE88-46F6-9D76-97C5CED46B8B}">
   <dimension ref="A1:E17"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="60.625" customWidth="1"/>
-    <col min="2" max="7" width="22.625" customWidth="1"/>
+    <col min="1" max="1" width="60.5625" customWidth="1"/>
+    <col min="2" max="7" width="22.5625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -2601,7 +2615,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:Z22"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="3" width="26" customWidth="1"/>
@@ -2655,7 +2669,7 @@
       <c r="I3" s="27"/>
       <c r="J3" s="27"/>
     </row>
-    <row r="4" spans="1:26" ht="30">
+    <row r="4" spans="1:26" ht="27.75">
       <c r="A4" s="1" t="s">
         <v>207</v>
       </c>
@@ -2809,7 +2823,7 @@
       <c r="I10" s="27"/>
       <c r="J10" s="27"/>
     </row>
-    <row r="11" spans="1:26" ht="30">
+    <row r="11" spans="1:26" ht="27.75">
       <c r="A11" s="1" t="s">
         <v>207</v>
       </c>
@@ -2909,7 +2923,7 @@
       <c r="I17" s="27"/>
       <c r="J17" s="27"/>
     </row>
-    <row r="18" spans="1:10" ht="114">
+    <row r="18" spans="1:10" ht="108">
       <c r="A18" s="2" t="s">
         <v>230</v>
       </c>
@@ -2975,7 +2989,7 @@
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
     </row>
-    <row r="21" spans="1:10" ht="28.5">
+    <row r="21" spans="1:10" ht="27">
       <c r="A21" s="2" t="s">
         <v>236</v>
       </c>
@@ -3002,13 +3016,13 @@
       <c r="I21" s="2"/>
       <c r="J21" s="2"/>
     </row>
-    <row r="22" spans="1:10" ht="99.75">
+    <row r="22" spans="1:10" ht="94.5">
       <c r="A22" s="2" t="s">
         <v>239</v>
       </c>
       <c r="B22" s="2" t="str">
         <f>"При заданных допущениях годовой объем цифрового рынка оценивается в диапазоне от "&amp;TEXT(J5,"# ##0")&amp;" до "&amp;TEXT(J7,"# ##0")&amp;" руб., а достижимая выручка нового бизнеса — от "&amp;TEXT(D12,"# ##0")&amp;" до "&amp;TEXT(D14,"# ##0")&amp;" руб. в год."</f>
-        <v>При заданных допущениях годовой объем цифрового рынка оценивается в диапазоне от 7 690 до 139 815 руб., а достижимая выручка нового бизнеса — от  38 до 4 894 руб. в год.</v>
+        <v>При заданных допущениях годовой объем цифрового рынка оценивается в диапазоне от 7 690 до 139 815 руб., а достижимая выручка нового бизнеса — от 38 до 4 894 руб. в год.</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
@@ -3037,7 +3051,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:Z22"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
@@ -3095,7 +3109,7 @@
       <c r="K3" s="27"/>
       <c r="L3" s="27"/>
     </row>
-    <row r="4" spans="1:26" ht="85.5">
+    <row r="4" spans="1:26" ht="81">
       <c r="A4" s="14" t="s">
         <v>242</v>
       </c>
@@ -3132,7 +3146,7 @@
         <v>25189.670000000002</v>
       </c>
     </row>
-    <row r="5" spans="1:26" ht="30">
+    <row r="5" spans="1:26" ht="27.75">
       <c r="A5" s="14" t="s">
         <v>247</v>
       </c>
@@ -3169,7 +3183,7 @@
         <v>Organic search</v>
       </c>
     </row>
-    <row r="6" spans="1:26" ht="30">
+    <row r="6" spans="1:26" ht="27.75">
       <c r="A6" s="14" t="s">
         <v>252</v>
       </c>
@@ -3199,13 +3213,13 @@
         <v>2033.8139558000003</v>
       </c>
     </row>
-    <row r="7" spans="1:26" ht="99.75">
+    <row r="7" spans="1:26" ht="94.5">
       <c r="A7" s="14" t="s">
         <v>256</v>
       </c>
       <c r="B7" s="15" t="str">
         <f>'06_Воронка_сценарии'!B22</f>
-        <v>При заданных допущениях годовой объем цифрового рынка оценивается в диапазоне от 7 690 до 139 815 руб., а достижимая выручка нового бизнеса — от  38 до 4 894 руб. в год.</v>
+        <v>При заданных допущениях годовой объем цифрового рынка оценивается в диапазоне от 7 690 до 139 815 руб., а достижимая выручка нового бизнеса — от 38 до 4 894 руб. в год.</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
@@ -3218,7 +3232,7 @@
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
     </row>
-    <row r="10" spans="1:26" ht="30">
+    <row r="10" spans="1:26" ht="27.75">
       <c r="A10" s="1" t="s">
         <v>207</v>
       </c>
@@ -3268,7 +3282,7 @@
         <v>4893.5262018300018</v>
       </c>
     </row>
-    <row r="16" spans="1:26" ht="15">
+    <row r="16" spans="1:26" ht="13.9">
       <c r="A16" s="1" t="s">
         <v>154</v>
       </c>
@@ -3370,7 +3384,7 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:Z24"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="36" customWidth="1"/>
@@ -3444,7 +3458,7 @@
         <v>269</v>
       </c>
       <c r="E4" s="3">
-        <v>46294.916666666664</v>
+        <v>46294.875</v>
       </c>
       <c r="F4" t="s">
         <v>270</v>
@@ -3464,7 +3478,7 @@
         <v>274</v>
       </c>
       <c r="E5" s="3">
-        <v>46294.916666666664</v>
+        <v>46294.875</v>
       </c>
       <c r="F5" t="s">
         <v>275</v>
@@ -3484,7 +3498,7 @@
         <v>279</v>
       </c>
       <c r="E6" s="3">
-        <v>46294.916666666664</v>
+        <v>46294.875</v>
       </c>
       <c r="F6" t="s">
         <v>280</v>
@@ -3504,7 +3518,7 @@
         <v>284</v>
       </c>
       <c r="E7" s="3">
-        <v>46294.916666666664</v>
+        <v>46294.875</v>
       </c>
       <c r="F7" t="s">
         <v>285</v>
@@ -3524,7 +3538,7 @@
         <v>289</v>
       </c>
       <c r="E8" s="3">
-        <v>46294.916666666664</v>
+        <v>46294.875</v>
       </c>
       <c r="F8" t="s">
         <v>290</v>
@@ -3544,7 +3558,7 @@
         <v>294</v>
       </c>
       <c r="E9" s="3">
-        <v>46294.916666666664</v>
+        <v>46294.875</v>
       </c>
       <c r="F9" t="s">
         <v>295</v>
@@ -3560,7 +3574,7 @@
       <c r="E12" s="27"/>
       <c r="F12" s="27"/>
     </row>
-    <row r="13" spans="1:26" ht="15">
+    <row r="13" spans="1:26" ht="13.9">
       <c r="A13" s="1" t="s">
         <v>297</v>
       </c>
@@ -3582,7 +3596,7 @@
     </row>
     <row r="14" spans="1:26">
       <c r="A14" s="3">
-        <v>46294.916666666664</v>
+        <v>46294.875</v>
       </c>
       <c r="B14" t="s">
         <v>305</v>
@@ -3602,7 +3616,7 @@
     </row>
     <row r="15" spans="1:26">
       <c r="A15" s="3">
-        <v>46294.916666666664</v>
+        <v>46294.875</v>
       </c>
       <c r="B15" t="s">
         <v>305</v>
@@ -3622,7 +3636,7 @@
     </row>
     <row r="16" spans="1:26">
       <c r="A16" s="3">
-        <v>46294.916666666664</v>
+        <v>46294.875</v>
       </c>
       <c r="B16" t="s">
         <v>305</v>
@@ -3642,7 +3656,7 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="3">
-        <v>46294.916666666664</v>
+        <v>46294.875</v>
       </c>
       <c r="B17" t="s">
         <v>305</v>
@@ -3662,7 +3676,7 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="3">
-        <v>46294.916666666664</v>
+        <v>46294.875</v>
       </c>
       <c r="B18" t="s">
         <v>305</v>
@@ -3682,7 +3696,7 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="23">
-        <v>46294.916666666664</v>
+        <v>46294.875</v>
       </c>
       <c r="B19" t="s">
         <v>309</v>
@@ -3702,7 +3716,7 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="23">
-        <v>46294.916666666664</v>
+        <v>46294.875</v>
       </c>
       <c r="B20" t="s">
         <v>369</v>
@@ -3722,7 +3736,7 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="23">
-        <v>46294.916666666664</v>
+        <v>46294.875</v>
       </c>
       <c r="B21" t="s">
         <v>371</v>
@@ -3759,12 +3773,12 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F27CB3D-2362-482A-B69D-9767DA53C7E1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E167DE7C-5FA1-468F-BF79-286D4C5B0382}">
   <dimension ref="A1:B20"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="60.625" customWidth="1"/>
-    <col min="2" max="7" width="22.625" customWidth="1"/>
+    <col min="1" max="1" width="60.5625" customWidth="1"/>
+    <col min="2" max="7" width="22.5625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -3918,12 +3932,12 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86094C7D-7D46-4305-861F-506B0FBD764E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DD4A868-3920-4730-8E20-BAE88A902F48}">
   <dimension ref="A1:K18"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="60.625" customWidth="1"/>
-    <col min="2" max="7" width="22.625" customWidth="1"/>
+    <col min="1" max="1" width="60.5625" customWidth="1"/>
+    <col min="2" max="7" width="22.5625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -4287,7 +4301,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Z18"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
@@ -4354,7 +4368,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:26" ht="42.75">
+    <row r="4" spans="1:26" ht="27">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
@@ -4380,7 +4394,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:26" ht="28.5">
+    <row r="5" spans="1:26" ht="27">
       <c r="A5" s="2" t="s">
         <v>17</v>
       </c>
@@ -4406,7 +4420,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:26" ht="28.5">
+    <row r="6" spans="1:26" ht="27">
       <c r="A6" s="2" t="s">
         <v>25</v>
       </c>
@@ -4432,7 +4446,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:26" ht="28.5">
+    <row r="7" spans="1:26" ht="27">
       <c r="A7" s="2" t="s">
         <v>32</v>
       </c>
@@ -4458,7 +4472,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="8" spans="1:26" ht="42.75">
+    <row r="8" spans="1:26" ht="40.5">
       <c r="A8" s="2" t="s">
         <v>40</v>
       </c>
@@ -4484,7 +4498,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="9" spans="1:26" ht="42.75">
+    <row r="9" spans="1:26" ht="27">
       <c r="A9" s="2" t="s">
         <v>48</v>
       </c>
@@ -4510,7 +4524,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="10" spans="1:26" ht="28.5">
+    <row r="10" spans="1:26" ht="27">
       <c r="A10" s="2" t="s">
         <v>56</v>
       </c>
@@ -4536,7 +4550,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="11" spans="1:26" ht="28.5">
+    <row r="11" spans="1:26" ht="27">
       <c r="A11" s="2" t="s">
         <v>64</v>
       </c>
@@ -4574,7 +4588,7 @@
       <c r="G13" s="27"/>
       <c r="H13" s="27"/>
     </row>
-    <row r="14" spans="1:26" ht="28.5">
+    <row r="14" spans="1:26" ht="27">
       <c r="A14" s="2" t="s">
         <v>73</v>
       </c>
@@ -4592,7 +4606,7 @@
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
     </row>
-    <row r="15" spans="1:26" ht="42.75">
+    <row r="15" spans="1:26" ht="40.5">
       <c r="A15" s="2" t="s">
         <v>77</v>
       </c>
@@ -4610,7 +4624,7 @@
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
     </row>
-    <row r="16" spans="1:26" ht="28.5">
+    <row r="16" spans="1:26" ht="27">
       <c r="A16" s="2" t="s">
         <v>81</v>
       </c>
@@ -4646,7 +4660,7 @@
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
     </row>
-    <row r="18" spans="1:8" ht="28.5">
+    <row r="18" spans="1:8" ht="27">
       <c r="A18" s="2" t="s">
         <v>89</v>
       </c>
@@ -4679,7 +4693,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Z20"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
@@ -4778,7 +4792,7 @@
         <v>106</v>
       </c>
       <c r="B7" s="3">
-        <v>46294.916666666664</v>
+        <v>46294.875</v>
       </c>
       <c r="C7" t="s">
         <v>107</v>
@@ -4958,7 +4972,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:Z27"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
@@ -5646,7 +5660,7 @@
       <c r="Q24" s="8"/>
       <c r="R24" s="8"/>
     </row>
-    <row r="25" spans="1:19" ht="15">
+    <row r="25" spans="1:19" ht="13.9">
       <c r="A25" s="6" t="s">
         <v>152</v>
       </c>
@@ -5794,7 +5808,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:Z11"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="2" width="18" customWidth="1"/>
     <col min="3" max="4" width="24" customWidth="1"/>
@@ -6091,7 +6105,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:Z9"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
@@ -6370,7 +6384,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:Z12"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
